--- a/benchmark_Results/benchmark_h1_h2_summary_simple.xlsx
+++ b/benchmark_Results/benchmark_h1_h2_summary_simple.xlsx
@@ -534,40 +534,40 @@
         <v>447</v>
       </c>
       <c r="F2" t="n">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="G2" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="H2" t="n">
-        <v>529</v>
+        <v>511</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8602941176470589</v>
+        <v>0.8694852941176471</v>
       </c>
       <c r="J2" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.825</v>
       </c>
       <c r="K2" t="n">
-        <v>0.2474226804123711</v>
+        <v>0.3402061855670103</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3870967741935484</v>
+        <v>0.4817518248175183</v>
       </c>
       <c r="M2" t="n">
-        <v>0.9932885906040269</v>
+        <v>0.9843400447427293</v>
       </c>
       <c r="N2" t="n">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="O2" t="n">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="P2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="Q2" t="n">
-        <v>73</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3">

--- a/benchmark_Results/benchmark_h1_h2_summary_simple.xlsx
+++ b/benchmark_Results/benchmark_h1_h2_summary_simple.xlsx
@@ -537,34 +537,34 @@
         <v>48</v>
       </c>
       <c r="G2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H2" t="n">
         <v>511</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8694852941176471</v>
+        <v>0.8676470588235294</v>
       </c>
       <c r="J2" t="n">
-        <v>0.825</v>
+        <v>0.8048780487804879</v>
       </c>
       <c r="K2" t="n">
         <v>0.3402061855670103</v>
       </c>
       <c r="L2" t="n">
-        <v>0.4817518248175183</v>
+        <v>0.4782608695652174</v>
       </c>
       <c r="M2" t="n">
-        <v>0.9843400447427293</v>
+        <v>0.9821029082774049</v>
       </c>
       <c r="N2" t="n">
         <v>33</v>
       </c>
       <c r="O2" t="n">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="P2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q2" t="n">
         <v>64</v>
@@ -589,31 +589,31 @@
         <v>447</v>
       </c>
       <c r="F3" t="n">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G3" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="H3" t="n">
         <v>511</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8823529411764706</v>
+        <v>0.875</v>
       </c>
       <c r="J3" t="n">
-        <v>0.9024390243902439</v>
+        <v>0.8918918918918919</v>
       </c>
       <c r="K3" t="n">
-        <v>0.3814432989690721</v>
+        <v>0.3402061855670103</v>
       </c>
       <c r="L3" t="n">
-        <v>0.536231884057971</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="M3" t="n">
         <v>0.9910514541387024</v>
       </c>
       <c r="N3" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="O3" t="n">
         <v>443</v>
@@ -622,7 +622,7 @@
         <v>4</v>
       </c>
       <c r="Q3" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>
